--- a/pacjenci/BOLESŁAW KOWALCZYK.xlsx
+++ b/pacjenci/BOLESŁAW KOWALCZYK.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>15.09.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>DLBCL - wznowa. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>całe ciało Akwizycję przeprowadzono  po 65min od podania 18F-FDG. Glikemia: 97mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DLBCL</t>
+          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 3,0; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego  W porównaniu do poprzedniego badania PET/CT z dnia 25.06.2024 - progresja wielkości nacieku w grzbietowo-dolnej części uda prawego.  Poza tym jak w opisie powyżej.  9.11.2020 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%. Problem kliniczny:  Chłoniak Hodgkina. Wczesna ocena odpowiedzi.   Konsultujący specjalista radiologii i diagnostyki obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Nieaktywne metabolicznie pojedyncze węzły chłonne szyjne wielkości do 12mm.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne przytchawicze dolne prawe i wnęki płuca prawego, SUV max do 3,1.  Mierne pobudzenie metaboliczne w topografii drobnego zwapnienia w okolicy przytchawiczej prawej, ponad cariną, SUV max 2,9. Pobudzenie metabolicze w topografii opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowymi zwapnieniami, SUV max do 4,0.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywna metaboliczna masa miękkotkankowa w środpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, SUV max do 1,9.  Oskrzele główne prawe i jego rozgałęzienia uciśnięte - wydatne obszary niedodmowo-naciekowe, zwłaszcza w płacie dolnym płuca prawego.  Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo, wielkości 83x49mm oraz w szczelinie międzypłatowej prawej. Zwiększona ilość płynu w prawej jamie opłucnowej, zarówno w płacie górnym jak i dolnym, o szerokości płaszcza do 102mm. Zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym.  Brzuch i miednica: Drobny aktywny metaboliczne węzeł chłonny biodrowy wewnętrzny prawy wielkości 8mm wg PET, SUV max 4,1 [Im 236].  Odcinkowe pobudzenie metaboliczne na przebiegu pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16mm i przyaortalne po stronie prawej wielkości do 20mm.  Miernie pogrubiałe nadnercze lewe. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 2,9.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Pobudzenie metabolicze w topografii opłucnej płuca prawego, w dolnych segmentach - do oceny z całością obrazu klinicznego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>19.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>23.03.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Stan po 6xABVD. Ocena stopnia remisji.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 90mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zgrubienia błony śluzowej w prawej zatoce czołowej - zatoka w znacznym stopniu bezpowietrzna. Zapalne zgrubienia błony śluzowej w sitowiu obustronnie - większe po stronie prawej. Nieaktywne metabolicznie pojedyncze węzły chłonne szyjne, wielkości do 12mm.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne przytchawicze dolne prawe, lewe, okna aortalno-płucnego, lewobocznie od aorty i wnęki płuca prawego, SUV max do 3,1.  Pobudzenie metaboliczne w topografii opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,6. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 36x34mm, z wydatnym zwapnieniem [SUV max do 2,0].  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo, oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 29mm. Zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Dokładna ocena zmian płucnych możliwa w badaniu TK KLP z kontrastem dożylnym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne na przebiegu pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16mm i przyaortalne po stronie prawej wielkości do 20mm.  Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,8 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej.  Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii opłucnej płuca prawego, w dolnych segmentach oraz węzłach chłonnych śródpiersia - do oceny z całością obrazu klinicznego i kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.8</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>15.06.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena aktywności choroby po zakończeniu zakończeniu leczenia.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  56 min od podania 18F-FDG. Glikemia: 101mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 37x30 mm, z wydatnym zwapnieniem SUV max do 1,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm], oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 16x28mm. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach SUV max do 3,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16x7 mm i przyaortalne  wielkości do 18mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 2,9 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,3.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono utrzymujące się pobudzenie metaboliczne w topografii opłucnej płuca prawego - do oceny z całością obrazu klinicznego i kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>20.09.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Stan po 8 cyklach ABVD przed RTGth.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 90mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetryczne pobudzenie metaboliczne w okolicy migdałka trąbkowego po stronie prawej - SUV max 4,0 - do kontroli laryngologicznej [Im fuz  42]  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Drobny obszar miękkotkankowy w zachyłku przeponowo-sercowym prawym wielkości 9mm wg PET, SUV max 3,1- do kontroli. Pobudzone metabolicznie zwapnienie przy ścianie przełyku wielkości 9mm, SUV max 4,0- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne przytchawicze prawe, wielkości ok. 17x13 mm, z wydatnym zwapnieniem - dokładniejsza ocena możliwa w badaniu TK z kontrastem.  Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm]. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 12x7 mm i przyaortalne wielkości do 16mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,0.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono utrzymujące się pobudzenie metaboliczne w topografii opłucnej płuca prawego - do oceny z całością obrazu klinicznego i kontroli. Drobny obszar miękkotkankowy w zachyłku przeponowo-sercowym prawym- do kontroli. Masa resztkowa do dalszej kontroli.   Poza tym jak w opisie powyżej.   1.08.2023 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 99mg%. Problem kliniczny:  Chłoniak Hodgkina. Spadek wydolności fizycznej, uporczywy świąd skóry.   Konsultujący specjalista radiologii i diagnostyki obrazowej:  Dr n. med. Agata Brzozowska-Czarnek   Głowa i szyja: Drobny pobudzony metabolicznie obszar w przyleganiu do dolnej części żuchwy wielkości 7mm wg PET, SUV max 3,6- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne:  - przy łuku aorty wielkości do 17mm, SUV max do 4,1; - przytchawicze dolne, podostrogowe i okna aortalno-płucnego wielkości do 11mm wg PET, SUV max do 3,2. Obustronnie w częściach grzbietowych obu płuc zmiany miąższowo-włókniste oraz odcinkowo pogrubiała opłucna, zwłaszcza po stronie lewej z obszarami zwiększonej aktywności metabolicznej wielkości do 15x18mm w wymiarze poprzecznym o długości do 73mm wg PET, SUV max do 6,2. Otorbiony płyn w lewej jamie opłucnej, przy przednio-lewobocznej ścianie KLP, wielkości do ok. 123x56mm ze zwiększoną aktywnością metaboliczną na obwodzie, SUV max do 7,2.  Pobudzone metabolicznie uwapnione węzły chłonne przy ścianie przełyku wielkości do 9mm, SUV max do 4,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne przytchawicze prawe, wielkości ok. 16x12 mm, z wydatnym zwapnieniem - dokładniejsza ocena możliwa w badaniu TK KLP z kontrastem dożylnym.  Drobne zwapnienia w okolicy przytchawiczej prawej. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Pęcherze rozedmowe, największy w szczycie płuca lewego wielkości 37x30mm.  Wydatne pasmowate  zmiany włókniste nadprzeponowo w płucu lewym. Odcinkowe zwapnienia na opłucnej. Poza powyższym - płyn w lewej jamie opłucnej o szerokości płaszcza do 19mm.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy w fazie i przeciwfazie oraz z kontrastem dożylnym. Nieregularne zwapnienia w śledzionie. Nerki o "pozaciąganych" pozapalnie obrysach. Drobne nieaktywne metabolicznie węzły chłonne pachwinowe.  Układ kostny: Aktywny metabolicznie obszar w topografii żebra I po stronie prawej z destrukcją tego żebra i przerwaniem jego ciągłości oraz z objęciem przyległych tkanek miękkich, SUV max 4,4. Aktywny metabolicznie obszar w przednim odcinku żebra I i II oraz w przednim i w grzbietowym odcinku żebra III po stronie lewej, SUV max 4,2 z przerwaniem ciągłości struktury kostnej. Aktywny metabolicznie obszar z rozległą destrukcją głowy kości ramiennej lewej i górnej części lewego obojczyka, z rozrzedzeniem struktury kostnej, SUV max do 5,7. Stan po przebytych złamaniach żeber IV i V lewych, z pobudzeniem metabolicznym, SUV max do 3,7.  Pobudzenie metaboliczne w małym stawie międzykręgowym na poziomie C3/C4 obustronnie, SUV max 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 2,9.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie obszary w grzbietowych częściach obu płuc oraz w topografii opłucnej - zwłaszcza w płucu lewym, zwiększoną aktywność metaboliczną wokół otorbionego płynu w lewym płucu i pobudzone metabolicznie węzły chłonne śródpiersia - do weryfikacji/ oceny z całością obrazu klinicznego. Widoczne są również aktywne i pobudzone metabolicznie obszary w żebrach oraz w strukturach lewego stawu barkowego, z ich częściową destrukcją.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>7.2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/BOLESŁAW KOWALCZYK.xlsx
+++ b/pacjenci/BOLESŁAW KOWALCZYK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>całe ciało Akwizycję przeprowadzono  po 65min od podania 18F-FDG. Glikemia: 97mg%.</t>
+          <t>całe ciało</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.  Brzuch i miednica: Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.  Układ kostny: Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.  Wartości referencyjne: MBPS SUVmax 3,0; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie pakiet węzłów chłonnych szyjnych grupy 2, 3 i 4 po stronie prawej,  wielkości wg PET 54x38x68 mm SUVmax 15,4. Aktywny metabolicznie węzeł chłonny szyjny prawy grupy 4/guzek płata prawego tarczycy, średnicy wg PET 15mm SUV max  7,4 - do oceny w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych. Stan po kraniektomii otworkowej w okolicy czołowej prawej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczycie płuca lewego. Niewielkie obwodowe zmiany włókniste w płatach górnych obu płuc. Pojedyncze drobne, obwodowe pęcherze rozedmowe w płacie dolnym płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo, większe po lewej.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rozlanie zwiększony metabolizm FDG w żołądku, SUV max do 5,9 - odczynowo? Aktywny metabolicznie węzeł chłonny pachwinowy prawy średnicy wg PET 10mm, SUV max 3,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W topografii/w ścisłym przyleganiu do górnego bieguna śledziony nadal widoczna jest miernie hypodensyjna w przeglądowym badaniu TK strefa wielkości ok. 22x20mm - zmiana w śledzionie? w przyleganiu do śledziony? - torbiel? -  jak poprzednio. Ok. 12mm śledziona dodatkowa. Drobna przepuklina okołopępkowa. Bardzo drobne uwapnione konkrementy w UKM-ie nerki lewej. Poza powyższym - dość liczne drobne i miernie wydatne węzły chłonne pachwinowe.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w topografii w grzbietowej części stawu kolanowego prawego SUV max 11,0 - w pierwszej kolejności zmiany odczynowo-przeciążeniowe. Miernie wzmożony metabolizm FDG w topografii stawów barkowych i biodrowych, SUV max do 3,6 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe.  Poza tym niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Rozległy naczyniak trzonu Th11. Niewielkie dyskopatie w odcinku szyjnym kregosłupa. Niewielka dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Drobne torbielki zwyrodnieniowe w głowach obu kości ramiennych. Wydatna wyspa kostna w grzbietowym odcinku żebra VIII lewego. Drobne wyspy kostne w kościach miednicy. Nieregularny obszar sklerotyzacji w trzonie lewej kości biodrowej, wielkości 17x11mm - zawał kostny? inne?  Inne: Aktywne metabolicznie węzły chłonne w dolnej części uda prawego oraz w okolicy kolana, średnicy wg PET do 15 mm SUV max 15,3. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego na łącznej długości wg PET  241mm, SUV max 19,6. Żylaki kończyn dolnych, więcej po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnej metabolicznie choroby chłoniakowej, z zajęciem węzłów chłonnych po obu stronach przepony. Rozlanie wzmożony metabolizm FDG w topografii struktur naczyniowych, żylnych? w grzbietowo-dolnej części uda prawego  W porównaniu do poprzedniego badania PET/CT z dnia 25.06.2024 - progresja wielkości nacieku w grzbietowo-dolnej części uda prawego.  Poza tym jak w opisie powyżej.  9.11.2020 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%. Problem kliniczny:  Chłoniak Hodgkina. Wczesna ocena odpowiedzi.   Konsultujący specjalista radiologii i diagnostyki obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Nieaktywne metabolicznie pojedyncze węzły chłonne szyjne wielkości do 12mm.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne przytchawicze dolne prawe i wnęki płuca prawego, SUV max do 3,1.  Mierne pobudzenie metaboliczne w topografii drobnego zwapnienia w okolicy przytchawiczej prawej, ponad cariną, SUV max 2,9. Pobudzenie metabolicze w topografii opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowymi zwapnieniami, SUV max do 4,0.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywna metaboliczna masa miękkotkankowa w środpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, SUV max do 1,9.  Oskrzele główne prawe i jego rozgałęzienia uciśnięte - wydatne obszary niedodmowo-naciekowe, zwłaszcza w płacie dolnym płuca prawego.  Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo, wielkości 83x49mm oraz w szczelinie międzypłatowej prawej. Zwiększona ilość płynu w prawej jamie opłucnowej, zarówno w płacie górnym jak i dolnym, o szerokości płaszcza do 102mm. Zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym.  Brzuch i miednica: Drobny aktywny metaboliczne węzeł chłonny biodrowy wewnętrzny prawy wielkości 8mm wg PET, SUV max 4,1 [Im 236].  Odcinkowe pobudzenie metaboliczne na przebiegu pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16mm i przyaortalne po stronie prawej wielkości do 20mm.  Miernie pogrubiałe nadnercze lewe. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 2,9.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Pobudzenie metabolicze w topografii opłucnej płuca prawego, w dolnych segmentach - do oceny z całością obrazu klinicznego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 90mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zgrubienia błony śluzowej w prawej zatoce czołowej - zatoka w znacznym stopniu bezpowietrzna. Zapalne zgrubienia błony śluzowej w sitowiu obustronnie - większe po stronie prawej. Nieaktywne metabolicznie pojedyncze węzły chłonne szyjne, wielkości do 12mm.   Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne przytchawicze dolne prawe, lewe, okna aortalno-płucnego, lewobocznie od aorty i wnęki płuca prawego, SUV max do 3,1.  Pobudzenie metaboliczne w topografii opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,6. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 36x34mm, z wydatnym zwapnieniem [SUV max do 2,0].  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo, oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 29mm. Zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Dokładna ocena zmian płucnych możliwa w badaniu TK KLP z kontrastem dożylnym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne na przebiegu pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16mm i przyaortalne po stronie prawej wielkości do 20mm.  Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,8 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej.  Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zgrubienia błony śluzowej w prawej zatoce czołowej - zatoka w znacznym stopniu bezpowietrzna. Zapalne zgrubienia błony śluzowej w sitowiu obustronnie - większe po stronie prawej. Nieaktywne metabolicznie pojedyncze węzły chłonne szyjne, wielkości do 12mm.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne przytchawicze dolne prawe, lewe, okna aortalno-płucnego, lewobocznie od aorty i wnęki płuca prawego, SUV max do 3,1.  Pobudzenie metaboliczne w topografii opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,6. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 36x34mm, z wydatnym zwapnieniem [SUV max do 2,0].  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo, oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 29mm. Zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym. Dokładna ocena zmian płucnych możliwa w badaniu TK KLP z kontrastem dożylnym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne na przebiegu pętli jelitowych- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16mm i przyaortalne po stronie prawej wielkości do 20mm.  Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,8 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono pobudzenie metaboliczne w topografii opłucnej płuca prawego, w dolnych segmentach oraz węzłach chłonnych śródpiersia - do oceny z całością obrazu klinicznego i kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  56 min od podania 18F-FDG. Glikemia: 101mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 37x30 mm, z wydatnym zwapnieniem SUV max do 1,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm], oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 16x28mm. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach SUV max do 3,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16x7 mm i przyaortalne  wielkości do 18mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 2,9 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 2,3.</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne śródpiersiowe i przytchawicze prawe, wielkości ok. 37x30 mm, z wydatnym zwapnieniem SUV max do 1,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm], oraz w szczelinie międzypłatowej prawej o szerokości płaszcza do 16x28mm. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach SUV max do 3,0- czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 16x7 mm i przyaortalne  wielkości do 18mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 2,9 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Ok. 3mm zwapnienie/ciało obce podskórnie na ścianie przedniej KLP, w okolicy obojczykowej prawej. Zwapnienia w tkance podskórnej przedniej ściany miednicy.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono utrzymujące się pobudzenie metaboliczne w topografii opłucnej płuca prawego - do oceny z całością obrazu klinicznego i kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  62min od podania 18F-FDG. Glikemia: 90mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetryczne pobudzenie metaboliczne w okolicy migdałka trąbkowego po stronie prawej - SUV max 4,0 - do kontroli laryngologicznej [Im fuz  42]  Klatka piersiowa i śródpiersie: Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Drobny obszar miękkotkankowy w zachyłku przeponowo-sercowym prawym wielkości 9mm wg PET, SUV max 3,1- do kontroli. Pobudzone metabolicznie zwapnienie przy ścianie przełyku wielkości 9mm, SUV max 4,0- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne przytchawicze prawe, wielkości ok. 17x13 mm, z wydatnym zwapnieniem - dokładniejsza ocena możliwa w badaniu TK z kontrastem.  Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm]. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 12x7 mm i przyaortalne wielkości do 16mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.  Układ kostny: Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,0.</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetryczne pobudzenie metaboliczne w okolicy migdałka trąbkowego po stronie prawej - SUV max 4,0 - do kontroli laryngologicznej [Im fuz  42]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii pogrubiałej opłucnej płuca prawego, w dolnych segmentach, z widocznymi odcinkowo zwapnieniami, SUV max do 3,4. Drobny obszar miękkotkankowy w zachyłku przeponowo-sercowym prawym wielkości 9mm wg PET, SUV max 3,1- do kontroli. Pobudzone metabolicznie zwapnienie przy ścianie przełyku wielkości 9mm, SUV max 4,0- do kontroli.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne przytchawicze prawe, wielkości ok. 17x13 mm, z wydatnym zwapnieniem - dokładniejsza ocena możliwa w badaniu TK z kontrastem.  Drobne zwapnienia w okolicy przytchawiczej prawej. Otorbiony płyn w prawej jamie opłucnowej, przykręgosłupowo [o szerokości płaszcza do 15mm]. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Ok. 14mm pęcherz rozedmowy w segm. 9 płuca prawego. Niewielkie zmiany włókniste nadprzeponowo w płucu lewym.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Odcinkowe pobudzenie metaboliczne w jelitach - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nieaktywne metabolicznie węzły chłonne pachwinowe wielkości do 12x7 mm i przyaortalne wielkości do 16mm. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy. Nerki o "pozaciąganych" pozapalnie obrysach. Pęcherz moczowy o pogrubiałej ścianie, ale słabo wypełniony - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w prawym małym stawie międzykręgowym na poziomie C3/C4, SUV max 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Zwapnienia w tkance podskórnej przedniej ściany miednicy.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono utrzymujące się pobudzenie metaboliczne w topografii opłucnej płuca prawego - do oceny z całością obrazu klinicznego i kontroli. Drobny obszar miękkotkankowy w zachyłku przeponowo-sercowym prawym- do kontroli. Masa resztkowa do dalszej kontroli.   Poza tym jak w opisie powyżej.   1.08.2023 Zakres badania:  od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 99mg%. Problem kliniczny:  Chłoniak Hodgkina. Spadek wydolności fizycznej, uporczywy świąd skóry.   Konsultujący specjalista radiologii i diagnostyki obrazowej:  Dr n. med. Agata Brzozowska-Czarnek   Głowa i szyja: Drobny pobudzony metabolicznie obszar w przyleganiu do dolnej części żuchwy wielkości 7mm wg PET, SUV max 3,6- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne:  - przy łuku aorty wielkości do 17mm, SUV max do 4,1; - przytchawicze dolne, podostrogowe i okna aortalno-płucnego wielkości do 11mm wg PET, SUV max do 3,2. Obustronnie w częściach grzbietowych obu płuc zmiany miąższowo-włókniste oraz odcinkowo pogrubiała opłucna, zwłaszcza po stronie lewej z obszarami zwiększonej aktywności metabolicznej wielkości do 15x18mm w wymiarze poprzecznym o długości do 73mm wg PET, SUV max do 6,2. Otorbiony płyn w lewej jamie opłucnej, przy przednio-lewobocznej ścianie KLP, wielkości do ok. 123x56mm ze zwiększoną aktywnością metaboliczną na obwodzie, SUV max do 7,2.  Pobudzone metabolicznie uwapnione węzły chłonne przy ścianie przełyku wielkości do 9mm, SUV max do 4,9.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu po stronie prawej obejmująca węzły chłonne przytchawicze prawe, wielkości ok. 16x12 mm, z wydatnym zwapnieniem - dokładniejsza ocena możliwa w badaniu TK KLP z kontrastem dożylnym.  Drobne zwapnienia w okolicy przytchawiczej prawej. Wydatne zmiany rozedmowo-włókniste w szczycie płuca prawego oraz mniejsze lewego. Ok. 4mm zwapnienie w segm. 2 płuca prawego. Wydatne zmiany włókniste przyśródpiersiowo i nadprzeponowo w płucu prawym. Pęcherze rozedmowe, największy w szczycie płuca lewego wielkości 37x30mm.  Wydatne pasmowate  zmiany włókniste nadprzeponowo w płucu lewym. Odcinkowe zwapnienia na opłucnej. Poza powyższym - płyn w lewej jamie opłucnej o szerokości płaszcza do 19mm.  Brzuch i miednica: Odcinkowe pobudzenie metaboliczne w jelitach - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Trzon nadnercza lewego pogrubiały do 20mm - do oceny w badaniu MR nadnerczy w fazie i przeciwfazie oraz z kontrastem dożylnym. Nieregularne zwapnienia w śledzionie. Nerki o "pozaciąganych" pozapalnie obrysach. Drobne nieaktywne metabolicznie węzły chłonne pachwinowe.  Układ kostny: Aktywny metabolicznie obszar w topografii żebra I po stronie prawej z destrukcją tego żebra i przerwaniem jego ciągłości oraz z objęciem przyległych tkanek miękkich, SUV max 4,4. Aktywny metabolicznie obszar w przednim odcinku żebra I i II oraz w przednim i w grzbietowym odcinku żebra III po stronie lewej, SUV max 4,2 z przerwaniem ciągłości struktury kostnej. Aktywny metabolicznie obszar z rozległą destrukcją głowy kości ramiennej lewej i górnej części lewego obojczyka, z rozrzedzeniem struktury kostnej, SUV max do 5,7. Stan po przebytych złamaniach żeber IV i V lewych, z pobudzeniem metabolicznym, SUV max do 3,7.  Pobudzenie metaboliczne w małym stawie międzykręgowym na poziomie C3/C4 obustronnie, SUV max 3,3 - w pierwszej kolejności zmiany zwyrodnieniowo-przeciążeniowe. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Cechy niestabilności i wielopoziomowo dyskopatie w odcinku szyjnym kręgosłupa. Torbielka zwyrodnieniowa w grzbietowej części trzonu C3. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Os sacrum arcuatum. Zwapnienia/ciała obce wokół lewego stawu ramiennego. Pojedyncze drobne zwapnienia przy obu kościach ramiennych.  Inne: Miażdżyca aorty i tętnic potomnych. Zwapnienia w tkance podskórnej przedniej ściany miednicy.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 2,9.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono aktywne metabolicznie obszary w grzbietowych częściach obu płuc oraz w topografii opłucnej - zwłaszcza w płucu lewym, zwiększoną aktywność metaboliczną wokół otorbionego płynu w lewym płucu i pobudzone metabolicznie węzły chłonne śródpiersia - do weryfikacji/ oceny z całością obrazu klinicznego. Widoczne są również aktywne i pobudzone metabolicznie obszary w żebrach oraz w strukturach lewego stawu barkowego, z ich częściową destrukcją.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>7.2</v>
       </c>
     </row>
